--- a/results/results_semen_china.xlsx
+++ b/results/results_semen_china.xlsx
@@ -1,21 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/Speciale/results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC948F5-F642-4D4B-9C8C-5F6945486141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3200" yWindow="8180" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>P50</t>
+  </si>
+  <si>
+    <t>P75</t>
+  </si>
+  <si>
+    <t>P90</t>
+  </si>
+  <si>
+    <t>P95</t>
+  </si>
+  <si>
+    <t>LOD</t>
+  </si>
+  <si>
+    <t>p0_motility_dk</t>
+  </si>
+  <si>
+    <t>meanlog_dk</t>
+  </si>
+  <si>
+    <t>sdlog_dk</t>
+  </si>
+  <si>
+    <t>p_detectable_dk</t>
+  </si>
+  <si>
+    <t>mean_exp_dk</t>
+  </si>
+  <si>
+    <t>median_dk</t>
+  </si>
+  <si>
+    <t>PAF_motility_med</t>
+  </si>
+  <si>
+    <t>PAF_motility_lo</t>
+  </si>
+  <si>
+    <t>PAF_motility_hi</t>
+  </si>
+  <si>
+    <t>PAF_infertility_med</t>
+  </si>
+  <si>
+    <t>PAF_infertility_lo</t>
+  </si>
+  <si>
+    <t>PAF_infertility_hi</t>
+  </si>
+  <si>
+    <t>AC_med</t>
+  </si>
+  <si>
+    <t>AC_lo</t>
+  </si>
+  <si>
+    <t>AC_hi</t>
+  </si>
+  <si>
+    <t>YLD_reconstructed_med</t>
+  </si>
+  <si>
+    <t>YLD_reconstructed_lo</t>
+  </si>
+  <si>
+    <t>YLD_reconstructed_hi</t>
+  </si>
+  <si>
+    <t>YLD_gbd_med</t>
+  </si>
+  <si>
+    <t>YLD_gbd_lo</t>
+  </si>
+  <si>
+    <t>YLD_gbd_hi</t>
+  </si>
+  <si>
+    <t>DALY_reconstructed_med</t>
+  </si>
+  <si>
+    <t>DALY_reconstructed_lo</t>
+  </si>
+  <si>
+    <t>DALY_reconstructed_hi</t>
+  </si>
+  <si>
+    <t>DALY_gbd_med</t>
+  </si>
+  <si>
+    <t>DALY_gbd_lo</t>
+  </si>
+  <si>
+    <t>DALY_gbd_hi</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +176,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,236 +473,239 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>P75</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P90</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>P95</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LOD</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>p0_motility</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>meanlog_dk</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>sdlog_dk</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>p_detectable_dk</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mean_exp_dk</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>median_dk</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>PAF_motility_med</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>PAF_motility_lo</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>PAF_motility_hi</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>PAF_infertility_med</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>PAF_infertility_lo</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>PAF_infertility_hi</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>AC_med</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>AC_lo</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>AC_hi</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>YLD_med</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>YLD_lo</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>YLD_hi</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>DALY_med</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>DALY_lo</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>DALY_hi</t>
-        </is>
+    <row r="1" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2017</v>
       </c>
       <c r="B2">
-        <v>0.08210000000000001</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="C2">
         <v>0.1719</v>
       </c>
       <c r="D2">
-        <v>0.3761</v>
+        <v>0.37609999999999999</v>
       </c>
       <c r="E2">
-        <v>0.9372</v>
+        <v>0.93720000000000003</v>
       </c>
       <c r="F2">
-        <v>3.1821</v>
+        <v>3.1821000000000002</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="H2">
-        <v>0.397454868304232</v>
+        <v>0.39745486830423199</v>
       </c>
       <c r="I2">
         <v>-1.760842366593333</v>
       </c>
       <c r="J2">
-        <v>1.128198796627725</v>
+        <v>1.1281987966277249</v>
       </c>
       <c r="K2">
-        <v>0.446622151400884</v>
+        <v>0.97172280262803568</v>
       </c>
       <c r="L2">
-        <v>0.32483883750715</v>
+        <v>0.32483883750714998</v>
       </c>
       <c r="M2">
         <v>0.1719</v>
       </c>
       <c r="N2">
-        <v>0.03036422294754333</v>
+        <v>2.5651566451153251E-2</v>
       </c>
       <c r="O2">
-        <v>0.0202929418932775</v>
+        <v>1.7016852044844821E-2</v>
       </c>
       <c r="P2">
-        <v>0.04049245019100736</v>
+        <v>3.4332075975979613E-2</v>
       </c>
       <c r="Q2">
-        <v>0.006023619702081451</v>
+        <v>1.0060921344502431E-2</v>
       </c>
       <c r="R2">
-        <v>0.003966642433126377</v>
+        <v>5.8625462478814738E-3</v>
       </c>
       <c r="S2">
-        <v>0.008319822711723974</v>
+        <v>1.572599268774726E-2</v>
       </c>
       <c r="T2">
-        <v>74.16264612518046</v>
+        <v>125.6089886208043</v>
       </c>
       <c r="U2">
-        <v>41.05224378882183</v>
+        <v>60.466199450219918</v>
       </c>
       <c r="V2">
-        <v>125.9638604412171</v>
+        <v>235.28224186864941</v>
       </c>
       <c r="W2">
-        <v>0.5701879118696976</v>
+        <v>1.000364678468084</v>
       </c>
       <c r="X2">
-        <v>0.2506052576266963</v>
+        <v>0.36594569718938291</v>
       </c>
       <c r="Y2">
-        <v>1.201854423482813</v>
+        <v>2.1901172784806162</v>
       </c>
       <c r="Z2">
-        <v>0.5701879118696976</v>
+        <v>0.82896227261826094</v>
       </c>
       <c r="AA2">
-        <v>0.2506052576266963</v>
+        <v>0.31631649240959259</v>
       </c>
       <c r="AB2">
-        <v>1.201854423482813</v>
+        <v>1.7402597724342319</v>
+      </c>
+      <c r="AC2">
+        <v>1.000364678468084</v>
+      </c>
+      <c r="AD2">
+        <v>0.36594569718938291</v>
+      </c>
+      <c r="AE2">
+        <v>2.1901172784806162</v>
+      </c>
+      <c r="AF2">
+        <v>0.82896227261826094</v>
+      </c>
+      <c r="AG2">
+        <v>0.31631649240959259</v>
+      </c>
+      <c r="AH2">
+        <v>1.7402597724342319</v>
       </c>
     </row>
   </sheetData>
